--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -97,7 +97,7 @@
     <t>13:39</t>
   </si>
   <si>
-    <t>Общи литри по продукт / КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
+    <t>Общи литри по продукт / КСУДПЛУ  СВ. ЙОАН  ЗЛАТОУСТ</t>
   </si>
   <si>
     <t>Продукт</t>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -167,7 +167,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,12 +177,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,17 +227,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,70 +46,28 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна</t>
+  </si>
+  <si>
+    <t>В6367ТА</t>
   </si>
   <si>
     <t>В5677ВН</t>
   </si>
   <si>
-    <t>В5832ХЕ</t>
-  </si>
-  <si>
-    <t>В6367ТА</t>
+    <t>78970155027720378</t>
   </si>
   <si>
     <t>78970155027720360</t>
   </si>
   <si>
-    <t>78970155027720352</t>
-  </si>
-  <si>
-    <t>78970155027720378</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
-  </si>
-  <si>
-    <t>DIESEL DOUBLE FILTERED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>08:59:00</t>
-  </si>
-  <si>
-    <t>14:39:00</t>
-  </si>
-  <si>
-    <t>17:13:00</t>
-  </si>
-  <si>
-    <t>15:14:00</t>
-  </si>
-  <si>
-    <t>3232097510 3232097510</t>
-  </si>
-  <si>
-    <t>3232099068 3232099068</t>
-  </si>
-  <si>
-    <t>3232440400 3232440400</t>
-  </si>
-  <si>
-    <t>3232577557 3232577557</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
@@ -532,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -541,17 +496,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -585,195 +537,150 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46175</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>76.88</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.66</v>
+      </c>
+      <c r="H2">
+        <v>127.62</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.69</v>
+      </c>
+      <c r="J2">
+        <v>129.93</v>
+      </c>
+      <c r="K2">
+        <v>153078</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46161</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3">
+        <v>100.01</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.61</v>
+      </c>
+      <c r="H3">
+        <v>161.02</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="J3">
+        <v>164.02</v>
+      </c>
+      <c r="K3">
+        <v>153755</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46184</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2">
-        <v>69.73</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2">
-        <v>1.72</v>
-      </c>
-      <c r="I2" s="1">
-        <v>119.94</v>
-      </c>
-      <c r="J2">
-        <v>1.75</v>
-      </c>
-      <c r="K2" s="1">
-        <v>122.03</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2">
-        <v>73010</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46161</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="E4" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>65.14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3">
-        <v>1.72</v>
-      </c>
-      <c r="I3" s="1">
-        <v>112.04</v>
-      </c>
-      <c r="J3">
-        <v>1.75</v>
-      </c>
-      <c r="K3" s="1">
-        <v>114</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3">
-        <v>10454</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46168</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="F4">
+        <v>64.83</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.59</v>
+      </c>
+      <c r="H4">
+        <v>103.08</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.62</v>
+      </c>
+      <c r="J4">
+        <v>105.02</v>
+      </c>
+      <c r="K4">
+        <v>73600</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="3">
+        <v>46188</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5">
+        <v>75</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.57</v>
+      </c>
+      <c r="H5">
+        <v>117.75</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="J5">
+        <v>120</v>
+      </c>
+      <c r="K5">
+        <v>154277</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>95.09</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4">
-        <v>1.69</v>
-      </c>
-      <c r="I4" s="1">
-        <v>160.7</v>
-      </c>
-      <c r="J4">
-        <v>1.72</v>
-      </c>
-      <c r="K4" s="1">
-        <v>163.55</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
-        <v>152438</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46171</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>60.04</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5">
-        <v>1.92</v>
-      </c>
-      <c r="I5" s="1">
-        <v>115.28</v>
-      </c>
-      <c r="J5">
-        <v>1.95</v>
-      </c>
-      <c r="K5" s="1">
-        <v>117.08</v>
-      </c>
-      <c r="L5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5">
-        <v>10948</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -781,82 +688,62 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:11">
       <c r="A9" s="5" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B10" s="7">
-        <v>229.96</v>
+        <v>316.72</v>
       </c>
       <c r="C10" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="8">
-        <v>1.7076</v>
+        <v>1.6086</v>
       </c>
       <c r="E10" s="7">
-        <v>392.68</v>
+        <v>509.47</v>
       </c>
       <c r="F10" s="7">
-        <v>399.58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="6" t="s">
+        <v>518.97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="7">
-        <v>60.04</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.9201</v>
-      </c>
-      <c r="E11" s="7">
-        <v>115.28</v>
-      </c>
-      <c r="F11" s="7">
-        <v>117.08</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="10">
-        <v>290</v>
-      </c>
-      <c r="C12" s="10">
+      <c r="B11" s="10">
+        <v>316.72</v>
+      </c>
+      <c r="C11" s="10">
         <v>4</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>507.96</v>
-      </c>
-      <c r="F12" s="10">
-        <v>516.66</v>
+      <c r="D11" s="8"/>
+      <c r="E11" s="10">
+        <v>509.47</v>
+      </c>
+      <c r="F11" s="10">
+        <v>518.97</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -46,13 +46,19 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Сливница</t>
   </si>
   <si>
-    <t>Варна</t>
+    <t>Варна Цар Освободител</t>
   </si>
   <si>
     <t>В6367ТА</t>
@@ -68,6 +74,18 @@
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>13:58</t>
+  </si>
+  <si>
+    <t>11:21</t>
+  </si>
+  <si>
+    <t>08:21</t>
+  </si>
+  <si>
+    <t>08:49</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
@@ -487,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -500,10 +518,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -537,22 +557,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46175</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>76.88</v>
@@ -569,25 +595,31 @@
       <c r="J2">
         <v>129.93</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2">
         <v>153078</v>
       </c>
+      <c r="M2">
+        <v>137787</v>
+      </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46182</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>100.01</v>
@@ -604,25 +636,31 @@
       <c r="J3">
         <v>164.02</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3">
         <v>153755</v>
       </c>
+      <c r="M3">
+        <v>273738</v>
+      </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46184</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4">
         <v>64.83</v>
@@ -639,25 +677,31 @@
       <c r="J4">
         <v>105.02</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4">
         <v>73600</v>
       </c>
+      <c r="M4">
+        <v>140819</v>
+      </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
         <v>46188</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5">
         <v>75</v>
@@ -674,13 +718,19 @@
       <c r="J5">
         <v>120</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5">
         <v>154277</v>
       </c>
+      <c r="M5">
+        <v>275313</v>
+      </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -688,18 +738,18 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>7</v>
@@ -708,9 +758,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B10" s="7">
         <v>316.72</v>
@@ -728,9 +778,9 @@
         <v>518.97</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" s="9" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B11" s="10">
         <v>316.72</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="23">
   <si>
     <t>Дата</t>
   </si>
@@ -49,43 +49,22 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна Цар Освободител</t>
+    <t>Варна Чайка</t>
   </si>
   <si>
     <t>В6367ТА</t>
   </si>
   <si>
-    <t>В5677ВН</t>
-  </si>
-  <si>
     <t>78970155027720378</t>
   </si>
   <si>
-    <t>78970155027720360</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>13:58</t>
-  </si>
-  <si>
-    <t>11:21</t>
-  </si>
-  <si>
-    <t>08:21</t>
-  </si>
-  <si>
-    <t>08:49</t>
+    <t>2026-06-19 10:51:01</t>
+  </si>
+  <si>
+    <t>2026-06-24 08:01:47</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
@@ -505,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -518,12 +497,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -557,248 +534,148 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>70.03</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H2">
+        <v>107.15</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J2">
+        <v>109.25</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46175</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46197</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3">
+        <v>40</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H3">
+        <v>59.6</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J3">
+        <v>60.8</v>
+      </c>
+      <c r="K3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F2">
-        <v>76.88</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.66</v>
-      </c>
-      <c r="H2">
-        <v>127.62</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="J2">
-        <v>129.93</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="L2">
-        <v>153078</v>
-      </c>
-      <c r="M2">
-        <v>137787</v>
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46182</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3">
-        <v>100.01</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.61</v>
-      </c>
-      <c r="H3">
-        <v>161.02</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="J3">
-        <v>164.02</v>
-      </c>
-      <c r="K3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3">
-        <v>153755</v>
-      </c>
-      <c r="M3">
-        <v>273738</v>
+      <c r="B8" s="7">
+        <v>110.03</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1.5155</v>
+      </c>
+      <c r="E8" s="7">
+        <v>166.75</v>
+      </c>
+      <c r="F8" s="7">
+        <v>170.05</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46184</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4">
-        <v>64.83</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.59</v>
-      </c>
-      <c r="H4">
-        <v>103.08</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="J4">
-        <v>105.02</v>
-      </c>
-      <c r="K4" t="s">
+    <row r="9" spans="1:11">
+      <c r="A9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L4">
-        <v>73600</v>
-      </c>
-      <c r="M4">
-        <v>140819</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3">
-        <v>46188</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5">
-        <v>75</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.57</v>
-      </c>
-      <c r="H5">
-        <v>117.75</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="J5">
-        <v>120</v>
-      </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5">
-        <v>154277</v>
-      </c>
-      <c r="M5">
-        <v>275313</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="7">
-        <v>316.72</v>
-      </c>
-      <c r="C10" s="7">
-        <v>4</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.6086</v>
-      </c>
-      <c r="E10" s="7">
-        <v>509.47</v>
-      </c>
-      <c r="F10" s="7">
-        <v>518.97</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="10">
-        <v>316.72</v>
-      </c>
-      <c r="C11" s="10">
-        <v>4</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="10">
-        <v>509.47</v>
-      </c>
-      <c r="F11" s="10">
-        <v>518.97</v>
+      <c r="B9" s="10">
+        <v>110.03</v>
+      </c>
+      <c r="C9" s="10">
+        <v>2</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="10">
+        <v>166.75</v>
+      </c>
+      <c r="F9" s="10">
+        <v>170.05</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,7 +52,16 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Чайка</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
   </si>
   <si>
     <t>В6367ТА</t>
@@ -61,10 +73,25 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-19 10:51:01</t>
-  </si>
-  <si>
-    <t>2026-06-24 08:01:47</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>10:50:00</t>
+  </si>
+  <si>
+    <t>08:01:00</t>
+  </si>
+  <si>
+    <t>06:52:00</t>
+  </si>
+  <si>
+    <t>3233581729 3233581729</t>
+  </si>
+  <si>
+    <t>3233784463 3233784463</t>
+  </si>
+  <si>
+    <t>3234037052 3234037052</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
@@ -484,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -493,14 +520,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -534,148 +564,219 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46192</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>70.03</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
         <v>1.53</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>107.15</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.56</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>109.25</v>
       </c>
-      <c r="K2" t="s">
-        <v>15</v>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2">
+        <v>545894</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46197</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F3">
         <v>40</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3">
         <v>1.49</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>59.6</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.52</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>60.8</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3">
+        <v>155266</v>
+      </c>
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46202</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
       </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>50</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4">
+        <v>1.48</v>
+      </c>
+      <c r="I4" s="1">
+        <v>74</v>
+      </c>
+      <c r="J4">
+        <v>1.51</v>
+      </c>
+      <c r="K4" s="1">
+        <v>75.5</v>
+      </c>
+      <c r="L4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4">
+        <v>555561</v>
+      </c>
+      <c r="N4" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+    <row r="7" spans="1:14">
+      <c r="A7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="5" t="s">
+    <row r="8" spans="1:14">
+      <c r="A8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
+      <c r="B9" s="7">
+        <v>160.03</v>
+      </c>
+      <c r="C9" s="7">
+        <v>3</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.5044</v>
+      </c>
+      <c r="E9" s="7">
+        <v>240.75</v>
+      </c>
+      <c r="F9" s="7">
+        <v>245.55</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="7">
-        <v>110.03</v>
-      </c>
-      <c r="C8" s="7">
-        <v>2</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1.5155</v>
-      </c>
-      <c r="E8" s="7">
-        <v>166.75</v>
-      </c>
-      <c r="F8" s="7">
-        <v>170.05</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" s="10">
-        <v>110.03</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="10">
-        <v>166.75</v>
-      </c>
-      <c r="F9" s="10">
-        <v>170.05</v>
+    <row r="10" spans="1:14">
+      <c r="A10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="10">
+        <v>160.03</v>
+      </c>
+      <c r="C10" s="10">
+        <v>3</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>240.75</v>
+      </c>
+      <c r="F10" s="10">
+        <v>245.55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,10 +55,10 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1158 Варна Чайка</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
   </si>
   <si>
     <t>В6367ТА</t>
@@ -73,25 +70,13 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>10:50:00</t>
-  </si>
-  <si>
-    <t>08:01:00</t>
-  </si>
-  <si>
-    <t>06:52:00</t>
-  </si>
-  <si>
-    <t>3233581729 3233581729</t>
-  </si>
-  <si>
-    <t>3233784463 3233784463</t>
-  </si>
-  <si>
-    <t>3234037052 3234037052</t>
+    <t>10:51</t>
+  </si>
+  <si>
+    <t>08:01</t>
+  </si>
+  <si>
+    <t>06:52</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
@@ -511,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,17 +505,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -570,145 +554,133 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46192</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
       </c>
       <c r="F2">
         <v>70.03</v>
       </c>
-      <c r="G2" t="s">
-        <v>19</v>
+      <c r="G2" s="1">
+        <v>1.53</v>
       </c>
       <c r="H2">
-        <v>1.53</v>
+        <v>107.15</v>
       </c>
       <c r="I2" s="1">
-        <v>107.15</v>
+        <v>1.56</v>
       </c>
       <c r="J2">
-        <v>1.56</v>
-      </c>
-      <c r="K2" s="1">
         <v>109.25</v>
       </c>
-      <c r="L2" t="s">
-        <v>20</v>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2">
+        <v>545894</v>
       </c>
       <c r="M2">
-        <v>545894</v>
-      </c>
-      <c r="N2" t="s">
-        <v>23</v>
+        <v>115442</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46197</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
       </c>
       <c r="F3">
         <v>40</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="H3">
+        <v>59.6</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J3">
+        <v>60.8</v>
+      </c>
+      <c r="K3" t="s">
         <v>19</v>
       </c>
-      <c r="H3">
-        <v>1.49</v>
-      </c>
-      <c r="I3" s="1">
-        <v>59.6</v>
-      </c>
-      <c r="J3">
-        <v>1.52</v>
-      </c>
-      <c r="K3" s="1">
-        <v>60.8</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
+      <c r="L3">
+        <v>155266</v>
       </c>
       <c r="M3">
-        <v>155266</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
+        <v>118012</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46202</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
       </c>
       <c r="F4">
         <v>50</v>
       </c>
-      <c r="G4" t="s">
-        <v>19</v>
+      <c r="G4" s="1">
+        <v>1.48</v>
       </c>
       <c r="H4">
-        <v>1.48</v>
+        <v>74</v>
       </c>
       <c r="I4" s="1">
-        <v>74</v>
+        <v>1.51</v>
       </c>
       <c r="J4">
-        <v>1.51</v>
-      </c>
-      <c r="K4" s="1">
         <v>75.5</v>
       </c>
-      <c r="L4" t="s">
-        <v>22</v>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4">
+        <v>555561</v>
       </c>
       <c r="M4">
-        <v>555561</v>
-      </c>
-      <c r="N4" t="s">
-        <v>25</v>
+        <v>50527</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -716,29 +688,29 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="7">
         <v>160.03</v>
@@ -756,9 +728,9 @@
         <v>245.55</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:13">
       <c r="A10" s="9" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B10" s="10">
         <v>160.03</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,13 +55,10 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>В5677ВН</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1146 Варна Сливница</t>
   </si>
   <si>
     <t>В6367ТА</t>
@@ -67,9 +67,6 @@
     <t>В5832ХЕ</t>
   </si>
   <si>
-    <t>78970155027720360</t>
-  </si>
-  <si>
     <t>78970155027720378</t>
   </si>
   <si>
@@ -79,19 +76,31 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-01 10:26:49</t>
-  </si>
-  <si>
-    <t>2026-07-02 08:46:10</t>
-  </si>
-  <si>
-    <t>2026-07-08 13:07:16</t>
-  </si>
-  <si>
-    <t>2026-07-14 10:19:31</t>
-  </si>
-  <si>
-    <t>2026-07-14 14:02:46</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>06:12:00</t>
+  </si>
+  <si>
+    <t>11:36:00</t>
+  </si>
+  <si>
+    <t>06:30:00</t>
+  </si>
+  <si>
+    <t>09:59:00</t>
+  </si>
+  <si>
+    <t>3235121019 3235121019</t>
+  </si>
+  <si>
+    <t>3235172051 3235172051</t>
+  </si>
+  <si>
+    <t>3235462238 3235462238</t>
+  </si>
+  <si>
+    <t>3235557148 3235557148</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
@@ -511,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,15 +529,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -565,268 +576,260 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46204</v>
+        <v>46224</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2">
+        <v>60</v>
+      </c>
+      <c r="G2" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>61.31</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.48</v>
-      </c>
       <c r="H2">
-        <v>90.73999999999999</v>
+        <v>1.65</v>
       </c>
       <c r="I2" s="1">
-        <v>1.51</v>
+        <v>99</v>
       </c>
       <c r="J2">
-        <v>92.58</v>
-      </c>
-      <c r="K2" t="s">
+        <v>1.68</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100.8</v>
+      </c>
+      <c r="L2" t="s">
         <v>21</v>
       </c>
-      <c r="L2">
-        <v>74080</v>
+      <c r="M2">
+        <v>157333</v>
+      </c>
+      <c r="N2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>46205</v>
+        <v>46225</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
       </c>
       <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>40</v>
+      </c>
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="F3">
-        <v>55</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.48</v>
-      </c>
       <c r="H3">
-        <v>81.40000000000001</v>
+        <v>1.66</v>
       </c>
       <c r="I3" s="1">
-        <v>1.51</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J3">
-        <v>83.05</v>
-      </c>
-      <c r="K3" t="s">
+        <v>1.69</v>
+      </c>
+      <c r="K3" s="1">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="L3" t="s">
         <v>22</v>
       </c>
-      <c r="L3">
-        <v>156070</v>
+      <c r="M3">
+        <v>11538</v>
+      </c>
+      <c r="N3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
-        <v>46211</v>
+        <v>46231</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>65</v>
+      </c>
+      <c r="G4" t="s">
         <v>20</v>
       </c>
-      <c r="F4">
-        <v>56.2</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.49</v>
-      </c>
       <c r="H4">
-        <v>83.73999999999999</v>
+        <v>1.72</v>
       </c>
       <c r="I4" s="1">
-        <v>1.52</v>
+        <v>111.8</v>
       </c>
       <c r="J4">
-        <v>85.42</v>
-      </c>
-      <c r="K4" t="s">
+        <v>1.75</v>
+      </c>
+      <c r="K4" s="1">
+        <v>113.75</v>
+      </c>
+      <c r="L4" t="s">
         <v>23</v>
       </c>
-      <c r="L4">
-        <v>156300</v>
+      <c r="M4">
+        <v>157952</v>
+      </c>
+      <c r="N4" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
-        <v>46217</v>
+        <v>46233</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
         <v>18</v>
       </c>
       <c r="E5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5">
+        <v>40</v>
+      </c>
+      <c r="G5" t="s">
         <v>20</v>
       </c>
-      <c r="F5">
-        <v>55.21</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.53</v>
-      </c>
       <c r="H5">
-        <v>84.47</v>
+        <v>1.73</v>
       </c>
       <c r="I5" s="1">
-        <v>1.56</v>
+        <v>69.2</v>
       </c>
       <c r="J5">
-        <v>86.13</v>
-      </c>
-      <c r="K5" t="s">
+        <v>1.76</v>
+      </c>
+      <c r="K5" s="1">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="L5" t="s">
         <v>24</v>
       </c>
-      <c r="L5">
-        <v>156830</v>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="3">
-        <v>46217</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" t="s">
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6">
-        <v>50</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H6">
-        <v>76.5</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J6">
-        <v>78</v>
-      </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6">
-        <v>11190</v>
+      <c r="B10" s="7">
+        <v>205</v>
+      </c>
+      <c r="C10" s="7">
+        <v>4</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1.6898</v>
+      </c>
+      <c r="E10" s="7">
+        <v>346.4</v>
+      </c>
+      <c r="F10" s="7">
+        <v>352.55</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="7">
-        <v>277.72</v>
-      </c>
-      <c r="C11" s="7">
-        <v>5</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.501</v>
-      </c>
-      <c r="E11" s="7">
-        <v>416.85</v>
-      </c>
-      <c r="F11" s="7">
-        <v>425.18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="10">
-        <v>277.72</v>
-      </c>
-      <c r="C12" s="10">
-        <v>5</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>416.85</v>
-      </c>
-      <c r="F12" s="10">
-        <v>425.18</v>
+    <row r="11" spans="1:14">
+      <c r="A11" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="10">
+        <v>205</v>
+      </c>
+      <c r="C11" s="10">
+        <v>4</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="10">
+        <v>346.4</v>
+      </c>
+      <c r="F11" s="10">
+        <v>352.55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -128,7 +128,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -800,7 +800,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="8">
-        <v>1.6898</v>
+        <v>1.689756</v>
       </c>
       <c r="E10" s="7">
         <v>346.4</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="36">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -520,7 +523,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -533,13 +536,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -582,186 +585,201 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46224</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>60</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2">
+        <v>1.564</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.65</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>99</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>1.68</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>100.8</v>
       </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N2">
         <v>157333</v>
       </c>
-      <c r="N2" t="s">
-        <v>25</v>
+      <c r="O2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46225</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3">
+        <v>1.588</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.66</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>66.40000000000001</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>1.69</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>67.59999999999999</v>
       </c>
-      <c r="L3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3">
+      <c r="M3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3">
         <v>11538</v>
       </c>
-      <c r="N3" t="s">
-        <v>26</v>
+      <c r="O3" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4" s="3">
         <v>46231</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4">
+        <v>1.653</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.72</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>111.8</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>1.75</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>113.75</v>
       </c>
-      <c r="L4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4">
+      <c r="M4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4">
         <v>157952</v>
       </c>
-      <c r="N4" t="s">
-        <v>27</v>
+      <c r="O4" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="A5" s="3">
         <v>46233</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5">
+        <v>1.674</v>
+      </c>
+      <c r="I5" s="1">
         <v>1.73</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>69.2</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>1.76</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>70.40000000000001</v>
       </c>
-      <c r="L5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5">
+      <c r="M5" t="s">
+        <v>25</v>
+      </c>
+      <c r="N5">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>28</v>
+      <c r="O5" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -769,29 +787,29 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:15">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" s="7">
         <v>205</v>
@@ -809,9 +827,9 @@
         <v>352.55</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:15">
       <c r="A11" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="10">
         <v>205</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -129,9 +126,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -225,10 +222,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -536,13 +533,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -585,201 +582,186 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46224</v>
       </c>
       <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>60</v>
       </c>
       <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>1.65</v>
+      </c>
+      <c r="I2" s="1">
+        <v>99</v>
+      </c>
+      <c r="J2">
+        <v>1.68</v>
+      </c>
+      <c r="K2" s="1">
+        <v>100.8</v>
+      </c>
+      <c r="L2" t="s">
         <v>21</v>
       </c>
-      <c r="H2">
-        <v>1.564</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="J2">
-        <v>99</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L2" s="1">
-        <v>100.8</v>
-      </c>
-      <c r="M2" t="s">
-        <v>22</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>157333</v>
       </c>
-      <c r="O2" t="s">
-        <v>26</v>
+      <c r="N2" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46225</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
       </c>
       <c r="F3">
         <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H3">
-        <v>1.588</v>
+        <v>1.66</v>
       </c>
       <c r="I3" s="1">
-        <v>1.66</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J3">
-        <v>66.40000000000001</v>
+        <v>1.69</v>
       </c>
       <c r="K3" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="L3" s="1">
         <v>67.59999999999999</v>
       </c>
-      <c r="M3" t="s">
-        <v>23</v>
-      </c>
-      <c r="N3">
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3">
         <v>11538</v>
       </c>
-      <c r="O3" t="s">
-        <v>27</v>
+      <c r="N3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
         <v>46231</v>
       </c>
       <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4">
         <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H4">
-        <v>1.653</v>
+        <v>1.72</v>
       </c>
       <c r="I4" s="1">
-        <v>1.72</v>
+        <v>111.8</v>
       </c>
       <c r="J4">
-        <v>111.8</v>
+        <v>1.75</v>
       </c>
       <c r="K4" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L4" s="1">
         <v>113.75</v>
       </c>
-      <c r="M4" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4">
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M4">
         <v>157952</v>
       </c>
-      <c r="O4" t="s">
-        <v>28</v>
+      <c r="N4" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
         <v>46233</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
       </c>
       <c r="F5">
         <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H5">
-        <v>1.674</v>
+        <v>1.73</v>
       </c>
       <c r="I5" s="1">
-        <v>1.73</v>
+        <v>69.2</v>
       </c>
       <c r="J5">
-        <v>69.2</v>
+        <v>1.76</v>
       </c>
       <c r="K5" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L5" s="1">
         <v>70.40000000000001</v>
       </c>
-      <c r="M5" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5">
+      <c r="L5" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
+      <c r="N5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -787,49 +769,49 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:14">
       <c r="A10" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="7">
         <v>205</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <v>4</v>
       </c>
       <c r="D10" s="8">
-        <v>1.689756</v>
-      </c>
-      <c r="E10" s="7">
+        <v>1.69</v>
+      </c>
+      <c r="E10" s="8">
         <v>346.4</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="8">
         <v>352.55</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14">
       <c r="A11" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="10">
         <v>205</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,7 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
+    <t>Варна Сливница</t>
   </si>
   <si>
     <t>В6367ТА</t>
@@ -67,40 +64,34 @@
     <t>В5832ХЕ</t>
   </si>
   <si>
+    <t>В5677ВН</t>
+  </si>
+  <si>
     <t>78970155027720378</t>
   </si>
   <si>
     <t>78970155027720352</t>
   </si>
   <si>
+    <t>78970155027720360</t>
+  </si>
+  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>06:12:00</t>
-  </si>
-  <si>
-    <t>11:36:00</t>
-  </si>
-  <si>
-    <t>06:30:00</t>
-  </si>
-  <si>
-    <t>09:59:00</t>
-  </si>
-  <si>
-    <t>3235121019 3235121019</t>
-  </si>
-  <si>
-    <t>3235172051 3235172051</t>
-  </si>
-  <si>
-    <t>3235462238 3235462238</t>
-  </si>
-  <si>
-    <t>3235557148 3235557148</t>
+    <t>10:09</t>
+  </si>
+  <si>
+    <t>08:56</t>
+  </si>
+  <si>
+    <t>06:32</t>
+  </si>
+  <si>
+    <t>11:01</t>
+  </si>
+  <si>
+    <t>06:39</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
@@ -126,9 +117,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -222,10 +213,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -520,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -529,17 +520,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -579,257 +569,283 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46224</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2">
-        <v>60</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
+        <v>62</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.76</v>
       </c>
       <c r="H2">
-        <v>1.65</v>
+        <v>109.12</v>
       </c>
       <c r="I2" s="1">
-        <v>99</v>
+        <v>1.79</v>
       </c>
       <c r="J2">
-        <v>1.68</v>
-      </c>
-      <c r="K2" s="1">
-        <v>100.8</v>
-      </c>
-      <c r="L2" t="s">
+        <v>110.98</v>
+      </c>
+      <c r="K2" t="s">
         <v>21</v>
       </c>
+      <c r="L2">
+        <v>158510</v>
+      </c>
       <c r="M2">
-        <v>157333</v>
-      </c>
-      <c r="N2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>158576</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46225</v>
+        <v>46241</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>40</v>
-      </c>
-      <c r="G3" t="s">
-        <v>20</v>
+        <v>45</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.77</v>
       </c>
       <c r="H3">
-        <v>1.66</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="I3" s="1">
-        <v>66.40000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J3">
-        <v>1.69</v>
-      </c>
-      <c r="K3" s="1">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="L3" t="s">
+        <v>81</v>
+      </c>
+      <c r="K3" t="s">
         <v>22</v>
       </c>
+      <c r="L3">
+        <v>12161</v>
+      </c>
       <c r="M3">
-        <v>11538</v>
-      </c>
-      <c r="N3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>160160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
-        <v>46231</v>
+        <v>46244</v>
       </c>
       <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>14</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4">
-        <v>65</v>
-      </c>
-      <c r="G4" t="s">
-        <v>20</v>
+        <v>62</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.77</v>
       </c>
       <c r="H4">
-        <v>1.72</v>
+        <v>109.74</v>
       </c>
       <c r="I4" s="1">
-        <v>111.8</v>
+        <v>1.8</v>
       </c>
       <c r="J4">
-        <v>1.75</v>
-      </c>
-      <c r="K4" s="1">
-        <v>113.75</v>
-      </c>
-      <c r="L4" t="s">
+        <v>111.6</v>
+      </c>
+      <c r="K4" t="s">
         <v>23</v>
       </c>
+      <c r="L4">
+        <v>159046</v>
+      </c>
       <c r="M4">
-        <v>157952</v>
-      </c>
-      <c r="N4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>161389</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
-        <v>46233</v>
+        <v>46245</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5">
-        <v>40</v>
-      </c>
-      <c r="G5" t="s">
+        <v>60.478</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.77</v>
+      </c>
+      <c r="H5">
+        <v>107.046</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="J5">
+        <v>108.86</v>
+      </c>
+      <c r="K5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5">
+        <v>74509</v>
+      </c>
+      <c r="M5">
+        <v>161960</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
         <v>20</v>
       </c>
-      <c r="H5">
-        <v>1.73</v>
-      </c>
-      <c r="I5" s="1">
-        <v>69.2</v>
-      </c>
-      <c r="J5">
+      <c r="F6">
+        <v>30</v>
+      </c>
+      <c r="G6" s="1">
         <v>1.76</v>
       </c>
-      <c r="K5" s="1">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="L5" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="H6">
+        <v>52.8</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.79</v>
+      </c>
+      <c r="J6">
+        <v>53.7</v>
+      </c>
+      <c r="K6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6">
+        <v>159565</v>
+      </c>
+      <c r="M6">
+        <v>58315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="5" t="s">
+      <c r="D10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="E10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="7">
+        <v>259.478</v>
+      </c>
+      <c r="C11" s="7">
+        <v>5</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1.76645</v>
+      </c>
+      <c r="E11" s="7">
+        <v>458.36</v>
+      </c>
+      <c r="F11" s="7">
+        <v>466.14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="7">
-        <v>205</v>
-      </c>
-      <c r="C10" s="8">
-        <v>4</v>
-      </c>
-      <c r="D10" s="8">
-        <v>1.69</v>
-      </c>
-      <c r="E10" s="8">
-        <v>346.4</v>
-      </c>
-      <c r="F10" s="8">
-        <v>352.55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="10">
-        <v>205</v>
-      </c>
-      <c r="C11" s="10">
-        <v>4</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="10">
-        <v>346.4</v>
-      </c>
-      <c r="F11" s="10">
-        <v>352.55</v>
+      <c r="B12" s="10">
+        <v>259.478</v>
+      </c>
+      <c r="C12" s="10">
+        <v>5</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="10">
+        <v>458.36</v>
+      </c>
+      <c r="F12" s="10">
+        <v>466.14</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="40">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,7 +58,10 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
+    <t>1146 Варна Сливница</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
   </si>
   <si>
     <t>В6367ТА</t>
@@ -64,34 +70,52 @@
     <t>В5832ХЕ</t>
   </si>
   <si>
-    <t>В5677ВН</t>
-  </si>
-  <si>
     <t>78970155027720378</t>
   </si>
   <si>
     <t>78970155027720352</t>
   </si>
   <si>
-    <t>78970155027720360</t>
-  </si>
-  <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>10:09</t>
-  </si>
-  <si>
-    <t>08:56</t>
-  </si>
-  <si>
-    <t>06:32</t>
-  </si>
-  <si>
-    <t>11:01</t>
-  </si>
-  <si>
-    <t>06:39</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>06:25:00</t>
+  </si>
+  <si>
+    <t>09:59:00</t>
+  </si>
+  <si>
+    <t>06:10:00</t>
+  </si>
+  <si>
+    <t>09:46:00</t>
+  </si>
+  <si>
+    <t>05:07:00</t>
+  </si>
+  <si>
+    <t>04:57:00</t>
+  </si>
+  <si>
+    <t>3236528218 3236528218</t>
+  </si>
+  <si>
+    <t>3236555141 3236555141</t>
+  </si>
+  <si>
+    <t>3236848447 3236848447</t>
+  </si>
+  <si>
+    <t>3236985225 3236985225</t>
+  </si>
+  <si>
+    <t>3237049086 3237049086</t>
+  </si>
+  <si>
+    <t>3237183195 3237183195</t>
   </si>
   <si>
     <t>Общи литри по продукт / КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ</t>
@@ -116,10 +140,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -199,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -213,10 +238,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -511,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,16 +547,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -569,60 +597,66 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46237</v>
+        <v>46252</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
         <v>20</v>
       </c>
       <c r="F2">
-        <v>62</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="H2">
-        <v>109.12</v>
+        <v>53</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1.677</v>
       </c>
       <c r="I2" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="J2">
-        <v>110.98</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2">
-        <v>158510</v>
+        <v>88.881</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="K2" s="1">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
       </c>
       <c r="M2">
-        <v>158576</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>159800</v>
+      </c>
+      <c r="N2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>46241</v>
+        <v>46252</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
@@ -630,78 +664,84 @@
       <c r="F3">
         <v>45</v>
       </c>
-      <c r="G3" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H3">
-        <v>79.65000000000001</v>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1.677</v>
       </c>
       <c r="I3" s="1">
+        <v>75.465</v>
+      </c>
+      <c r="J3" s="1">
         <v>1.8</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>81</v>
       </c>
-      <c r="K3" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3">
-        <v>12161</v>
+      <c r="L3" t="s">
+        <v>23</v>
       </c>
       <c r="M3">
-        <v>160160</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>12455</v>
+      </c>
+      <c r="N3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4">
-        <v>62</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H4">
-        <v>109.74</v>
+        <v>55</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.708</v>
       </c>
       <c r="I4" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J4">
-        <v>111.6</v>
-      </c>
-      <c r="K4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4">
-        <v>159046</v>
+        <v>93.94</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="K4" s="1">
+        <v>101.75</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
       </c>
       <c r="M4">
-        <v>161389</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>160290</v>
+      </c>
+      <c r="N4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3">
-        <v>46245</v>
+        <v>46261</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
@@ -710,142 +750,192 @@
         <v>20</v>
       </c>
       <c r="F5">
-        <v>60.478</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="H5">
-        <v>107.046</v>
+        <v>50</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1.719</v>
       </c>
       <c r="I5" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="J5">
-        <v>108.86</v>
-      </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5">
-        <v>74509</v>
+        <v>85.95</v>
+      </c>
+      <c r="J5" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="K5" s="1">
+        <v>92.5</v>
+      </c>
+      <c r="L5" t="s">
+        <v>25</v>
       </c>
       <c r="M5">
-        <v>161960</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>12829</v>
+      </c>
+      <c r="N5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3">
-        <v>46248</v>
+        <v>46262</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
         <v>20</v>
       </c>
       <c r="F6">
-        <v>30</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="H6">
-        <v>52.8</v>
+        <v>80</v>
+      </c>
+      <c r="G6" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.719</v>
       </c>
       <c r="I6" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="J6">
-        <v>53.7</v>
-      </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L6">
-        <v>159565</v>
+        <v>137.52</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="K6" s="1">
+        <v>148</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
       </c>
       <c r="M6">
-        <v>58315</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="5" t="s">
+        <v>160810</v>
+      </c>
+      <c r="N6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="3">
+        <v>46265</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7">
+        <v>33</v>
+      </c>
+      <c r="G7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1.719</v>
+      </c>
+      <c r="I7" s="1">
+        <v>56.727</v>
+      </c>
+      <c r="J7" s="1">
+        <v>1.84</v>
+      </c>
+      <c r="K7" s="1">
+        <v>60.72</v>
+      </c>
+      <c r="L7" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="6" t="s">
+      <c r="M7">
+        <v>160940</v>
+      </c>
+      <c r="N7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="7">
-        <v>259.478</v>
-      </c>
-      <c r="C11" s="7">
-        <v>5</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.76645</v>
-      </c>
-      <c r="E11" s="7">
-        <v>458.36</v>
-      </c>
-      <c r="F11" s="7">
-        <v>466.14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="10">
-        <v>259.478</v>
-      </c>
-      <c r="C12" s="10">
-        <v>5</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>458.36</v>
-      </c>
-      <c r="F12" s="10">
-        <v>466.14</v>
+      <c r="B12" s="7">
+        <v>316</v>
+      </c>
+      <c r="C12" s="8">
+        <v>6</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1.70406</v>
+      </c>
+      <c r="E12" s="7">
+        <v>538.48</v>
+      </c>
+      <c r="F12" s="7">
+        <v>579.37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="11">
+        <v>316</v>
+      </c>
+      <c r="C13" s="12">
+        <v>6</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="11">
+        <v>538.48</v>
+      </c>
+      <c r="F13" s="11">
+        <v>579.37</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ/КСУДПЛУ СВ. ЙОАН ЗЛАТОУСТ.xlsx
@@ -624,10 +624,10 @@
         <v>21</v>
       </c>
       <c r="H2" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I2" s="1">
-        <v>88.881</v>
+        <v>93.81</v>
       </c>
       <c r="J2" s="1">
         <v>1.8</v>
@@ -668,10 +668,10 @@
         <v>21</v>
       </c>
       <c r="H3" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I3" s="1">
-        <v>75.465</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="J3" s="1">
         <v>1.8</v>
@@ -712,10 +712,10 @@
         <v>21</v>
       </c>
       <c r="H4" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I4" s="1">
-        <v>93.94</v>
+        <v>100.1</v>
       </c>
       <c r="J4" s="1">
         <v>1.85</v>
@@ -756,10 +756,10 @@
         <v>21</v>
       </c>
       <c r="H5" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I5" s="1">
-        <v>85.95</v>
+        <v>91</v>
       </c>
       <c r="J5" s="1">
         <v>1.85</v>
@@ -800,10 +800,10 @@
         <v>21</v>
       </c>
       <c r="H6" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I6" s="1">
-        <v>137.52</v>
+        <v>145.6</v>
       </c>
       <c r="J6" s="1">
         <v>1.85</v>
@@ -844,10 +844,10 @@
         <v>21</v>
       </c>
       <c r="H7" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I7" s="1">
-        <v>56.727</v>
+        <v>59.73</v>
       </c>
       <c r="J7" s="1">
         <v>1.84</v>
@@ -906,10 +906,10 @@
         <v>6</v>
       </c>
       <c r="D12" s="9">
-        <v>1.70406</v>
+        <v>1.80345</v>
       </c>
       <c r="E12" s="7">
-        <v>538.48</v>
+        <v>569.89</v>
       </c>
       <c r="F12" s="7">
         <v>579.37</v>
@@ -927,7 +927,7 @@
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="11">
-        <v>538.48</v>
+        <v>569.89</v>
       </c>
       <c r="F13" s="11">
         <v>579.37</v>
